--- a/Datas/Global.xlsx
+++ b/Datas/Global.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -105,7 +105,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,13 +120,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -271,18 +264,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -636,52 +623,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
@@ -696,87 +686,78 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1142,12 +1123,12 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1165,12 +1146,12 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1188,12 +1169,12 @@
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1205,35 +1186,35 @@
       </c>
     </row>
     <row r="5" ht="96" customHeight="1" spans="1:9">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>10</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>15</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>20</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>90</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <v>100</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="17.25" spans="8:9">
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
+    <row r="6" ht="17.25" spans="1:9">
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Datas/Global.xlsx
+++ b/Datas/Global.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -46,6 +46,9 @@
     <t>MeatToThreeKPCoinRate</t>
   </si>
   <si>
+    <t>PointRewardAmount</t>
+  </si>
+  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
   </si>
   <si>
     <t>肉/三千盘金币汇率</t>
+  </si>
+  <si>
+    <t>积分获得量</t>
   </si>
   <si>
     <t>注释</t>
@@ -1083,17 +1089,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="5" width="8.625" customWidth="1"/>
     <col min="6" max="6" width="28.625" customWidth="1"/>
     <col min="7" max="7" width="36.625" customWidth="1"/>
-    <col min="8" max="9" width="28.625" customWidth="1"/>
+    <col min="8" max="10" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9">
+    <row r="1" ht="28" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1115,77 +1121,89 @@
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:9">
+    <row r="2" ht="28" customHeight="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:9">
+    <row r="3" ht="28" customHeight="1" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:9">
+    <row r="4" ht="28" customHeight="1" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" ht="96" customHeight="1" spans="1:9">
+    <row r="5" ht="96" customHeight="1" spans="1:10">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>1</v>
@@ -1200,21 +1218,25 @@
         <v>20</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" s="4">
         <v>90</v>
       </c>
       <c r="H5" s="5">
-        <v>100</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" ht="17.25" spans="1:9">
+    <row r="6" ht="17.25" spans="8:10">
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Datas/Global.xlsx
+++ b/Datas/Global.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -49,6 +49,9 @@
     <t>PointRewardAmount</t>
   </si>
   <si>
+    <t>HiddenMapProbability</t>
+  </si>
+  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
   </si>
   <si>
     <t>积分获得量</t>
+  </si>
+  <si>
+    <t>隐藏地图概率</t>
   </si>
   <si>
     <t>注释</t>
@@ -1089,17 +1095,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="2" width="28.625" customWidth="1"/>
     <col min="3" max="5" width="8.625" customWidth="1"/>
     <col min="6" max="6" width="28.625" customWidth="1"/>
     <col min="7" max="7" width="36.625" customWidth="1"/>
-    <col min="8" max="10" width="28.625" customWidth="1"/>
+    <col min="8" max="11" width="28.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10">
+    <row r="1" ht="28" customHeight="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1124,86 +1130,98 @@
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:10">
+    <row r="2" ht="28" customHeight="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:10">
+    <row r="3" ht="28" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:10">
+    <row r="4" ht="28" customHeight="1" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" ht="96" customHeight="1" spans="1:10">
+    <row r="5" ht="96" customHeight="1" spans="1:11">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>1</v>
@@ -1218,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G5" s="4">
         <v>90</v>
@@ -1229,14 +1247,18 @@
       <c r="I5" s="5">
         <v>3</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>21</v>
+      <c r="J5" s="5">
+        <v>100</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6" ht="17.25" spans="8:10">
+    <row r="6" ht="17.25" spans="1:11">
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Datas/Global.xlsx
+++ b/Datas/Global.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -52,7 +52,7 @@
     <t>HiddenMapProbability</t>
   </si>
   <si>
-    <t>Comment</t>
+    <t>PropPrice</t>
   </si>
   <si>
     <t>##type</t>
@@ -67,9 +67,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -94,17 +91,13 @@
     <t>隐藏地图概率</t>
   </si>
   <si>
-    <t>注释</t>
+    <t>道具价格</t>
   </si>
   <si>
     <t>备注(从左往右):
 任务起始派发时间
 任务派发间隔
 任务持续时间</t>
-  </si>
-  <si>
-    <t>我给全家打肉吃
-全局配置表</t>
   </si>
 </sst>
 </file>
@@ -1160,65 +1153,65 @@
         <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" ht="96" customHeight="1" spans="1:11">
@@ -1230,16 +1223,16 @@
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E5" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H5" s="5">
         <v>10</v>
@@ -1248,13 +1241,13 @@
         <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>100</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>23</v>
+        <v>75</v>
+      </c>
+      <c r="K5" s="5">
+        <v>15</v>
       </c>
     </row>
-    <row r="6" ht="17.25" spans="1:11">
+    <row r="6" ht="17.25" spans="8:11">
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
